--- a/backend/Data/Resources/initial-data.xlsx
+++ b/backend/Data/Resources/initial-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.foerster\Documents\Projects\holidayhomes\backend\Data\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836952DE-BA3E-4C94-B4B8-1DE5F4EDE04A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85C5E14-C4CB-40AE-AAD1-935E35F07812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
